--- a/doc_testbed/Cape25e_pre-deployment-tests.xlsx
+++ b/doc_testbed/Cape25e_pre-deployment-tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hans\Documents\GitHub\shepherd_v2_planning\doc_testbed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBFD87B-2DD1-48C7-8DF8-8E6209376F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F97337-B321-4C8D-92F6-7121619C39B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="4296" windowWidth="21540" windowHeight="18600" xr2:uid="{0961F1A4-98B1-4F35-911A-F9CB780BF838}"/>
+    <workbookView xWindow="13332" yWindow="1560" windowWidth="19632" windowHeight="22932" xr2:uid="{0961F1A4-98B1-4F35-911A-F9CB780BF838}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="48">
   <si>
     <t>Notes</t>
   </si>
@@ -48,27 +48,12 @@
     <t>Cleaned</t>
   </si>
   <si>
-    <t>Dplm_Bbone</t>
-  </si>
-  <si>
-    <t>Dplm_Target</t>
-  </si>
-  <si>
-    <t>Dplm_Room</t>
-  </si>
-  <si>
-    <t>Dplm_Socket</t>
-  </si>
-  <si>
     <t>Cape</t>
   </si>
   <si>
     <t>1PI5</t>
   </si>
   <si>
-    <t>PI5-IC 11x Wrong</t>
-  </si>
-  <si>
     <t>11PI5</t>
   </si>
   <si>
@@ -78,22 +63,119 @@
     <t>I_On</t>
   </si>
   <si>
-    <t>Test_Emu</t>
-  </si>
-  <si>
-    <t>Test_GPIO</t>
-  </si>
-  <si>
-    <t>Test_TP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> U47 - PI5-IC shifted -&gt; Fixable</t>
-  </si>
-  <si>
     <t>15mA</t>
   </si>
   <si>
     <t>7V@~300mA EMU (350mA max @prep)</t>
+  </si>
+  <si>
+    <t>R@U5 &amp; U49 -&gt; fixed</t>
+  </si>
+  <si>
+    <t>L5V is only 4.96 V</t>
+  </si>
+  <si>
+    <t>TPorts added manually
+PRU0-1 LED on side</t>
+  </si>
+  <si>
+    <t>TP-A: bent pin -3 (GND)</t>
+  </si>
+  <si>
+    <t>TP-A: bent pins -10L (GPIO10), 
+-4R (Prog2 CLK)</t>
+  </si>
+  <si>
+    <t>P2 is missing on 2517 to 2530</t>
+  </si>
+  <si>
+    <t>preTest &amp; prep for 6capes takes 2h</t>
+  </si>
+  <si>
+    <t>PI5-IC 11x Wrong (PnP setup wrong)</t>
+  </si>
+  <si>
+    <t>(OK)</t>
+  </si>
+  <si>
+    <t>4PI</t>
+  </si>
+  <si>
+    <t>Test_Prog_A1</t>
+  </si>
+  <si>
+    <t>Test_Prog_A2</t>
+  </si>
+  <si>
+    <t>Test_Emu_A</t>
+  </si>
+  <si>
+    <t>Test_Emu_B</t>
+  </si>
+  <si>
+    <t>Test_Prog_B1</t>
+  </si>
+  <si>
+    <t>Test_Prog_B2</t>
+  </si>
+  <si>
+    <t>Test_GPIO_A</t>
+  </si>
+  <si>
+    <t>Test_GPIO_B</t>
+  </si>
+  <si>
+    <t>GPIO5</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>TP-A: bent pins -7R (NC), -1R (L3V3), 
+-3R (prog2 IO)</t>
+  </si>
+  <si>
+    <t>TP-A: slightly shifted U37 &amp; U16, U46 PGL,
+TP-B: slightly shifted U40, U49 PGH</t>
+  </si>
+  <si>
+    <t>U48/Pi5/GPIO11 -&gt; fixed</t>
+  </si>
+  <si>
+    <t>48/64/54</t>
+  </si>
+  <si>
+    <t>49/63/54</t>
+  </si>
+  <si>
+    <t>60/55</t>
+  </si>
+  <si>
+    <t>59-75</t>
+  </si>
+  <si>
+    <t>57/63</t>
+  </si>
+  <si>
+    <t>U43 looks shifted, but is not</t>
+  </si>
+  <si>
+    <t>TP-B MSP fails to program
+Check U29, U40, U43, U29 &amp; U24, TODO</t>
+  </si>
+  <si>
+    <t>TP-B  MSP fails to program
+Check U29, U40, U43, U29 &amp; U24, TODO</t>
+  </si>
+  <si>
+    <t>C @ U5 shifted -&gt; fixed</t>
+  </si>
+  <si>
+    <t>U47/PI5 shifted -&gt; Fixed
+TP-A GPIO5 defective -&gt; TODO</t>
   </si>
 </sst>
 </file>
@@ -123,7 +205,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +224,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -155,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -163,23 +251,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -257,25 +360,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AD7FE81-A7F6-4917-AEFC-78F3D59AF956}" name="Table1" displayName="Table1" ref="A1:P31" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A1:P31" xr:uid="{3AD7FE81-A7F6-4917-AEFC-78F3D59AF956}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{AB1111EA-1189-4670-B60E-2E04180241E7}" name="Cape" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{9C88A57E-F780-4CC3-BA99-046F311B4956}" name="Visual" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{7195CB4D-4AF3-465C-AF5A-354CCBF97D0C}" name="I_Off" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{2CC13D68-4199-4EB2-B005-409CEE8AEA08}" name="I_On" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{94650C81-E1B2-4E5C-8E32-27458281274E}" name="Add_Caps" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{4F9009E0-8056-4545-95BD-48D33DC9717D}" name="Add_Hdr" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{1D628D7A-B725-444C-A77B-0CA23F68FD1C}" name="Cleaned" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{383AAC32-63FB-4BEC-BCC1-92C187B19C3C}" name="Test_Emu" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{A8AD316B-14A4-40BE-93E9-CA8ED8D5B6FD}" name="Test_GPIO" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{ABBB3684-2D1E-4E68-B56A-D2C741B0CB3A}" name="Test_TP2" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{126B0F9E-2DEB-4F91-8378-718C5F0ADC82}" name="Cal_Emu" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{4BB433E8-BB2C-434A-86F8-CAD847215D39}" name="Dplm_Bbone" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{FF2AF165-23D6-4020-80AF-07BF1E63D03B}" name="Dplm_Target" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{5B80B321-6B6C-41B8-AE7E-C24D9A411E6E}" name="Dplm_Room" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{B0B7780B-D915-49CD-86B4-61AE16185936}" name="Dplm_Socket" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{9C254D40-B1FA-4933-8C96-05EFD55C114C}" name="Notes" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AD7FE81-A7F6-4917-AEFC-78F3D59AF956}" name="Table1" displayName="Table1" ref="A1:Q33" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q33" xr:uid="{3AD7FE81-A7F6-4917-AEFC-78F3D59AF956}"/>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{AB1111EA-1189-4670-B60E-2E04180241E7}" name="Cape" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{9C88A57E-F780-4CC3-BA99-046F311B4956}" name="Visual" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{7195CB4D-4AF3-465C-AF5A-354CCBF97D0C}" name="I_Off" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{2CC13D68-4199-4EB2-B005-409CEE8AEA08}" name="I_On" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{94650C81-E1B2-4E5C-8E32-27458281274E}" name="Add_Caps" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{4F9009E0-8056-4545-95BD-48D33DC9717D}" name="Add_Hdr" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{1D628D7A-B725-444C-A77B-0CA23F68FD1C}" name="Cleaned" dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{1F026C48-F542-4668-8478-72159AA5842E}" name="Test_Prog_A1" dataDxfId="9"/>
+    <tableColumn id="21" xr3:uid="{D0B915E6-D566-4563-B4BD-0FAB697DBCAD}" name="Test_Prog_A2" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{E7300B17-D9CF-4580-9CE3-2A0FA61BDE0B}" name="Test_Prog_B1" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{A9F8AB9C-8741-40DC-95C0-C0FD5AFDFE29}" name="Test_Prog_B2" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{3B5425C3-04E3-4299-AB07-1129BF2962D5}" name="Test_Emu_A" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{383AAC32-63FB-4BEC-BCC1-92C187B19C3C}" name="Test_Emu_B" dataDxfId="4"/>
+    <tableColumn id="22" xr3:uid="{89C77B7B-15E5-46E4-A394-28EC3CF7130E}" name="Test_GPIO_A" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{A8AD316B-14A4-40BE-93E9-CA8ED8D5B6FD}" name="Test_GPIO_B" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{126B0F9E-2DEB-4F91-8378-718C5F0ADC82}" name="Cal_Emu" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{9C254D40-B1FA-4933-8C96-05EFD55C114C}" name="Notes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -581,29 +685,28 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.109375" customWidth="1"/>
     <col min="2" max="3" width="6.44140625" customWidth="1"/>
     <col min="4" max="4" width="7.109375" customWidth="1"/>
-    <col min="5" max="11" width="6.44140625" customWidth="1"/>
-    <col min="12" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="40" customWidth="1"/>
+    <col min="5" max="16" width="5.5546875" customWidth="1"/>
+    <col min="17" max="17" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="74.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="74.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -615,42 +718,45 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>2501</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
-        <v>2501</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1">
         <v>55</v>
@@ -666,22 +772,23 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>2502</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="C3" s="1">
         <v>15</v>
       </c>
       <c r="D3" s="1">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -694,12 +801,13 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>2503</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -724,559 +832,1415 @@
       <c r="I4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="J4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
         <v>2504</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1">
+        <v>63</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="P5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>2505</v>
       </c>
       <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="C6" s="1">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1">
+        <v>56</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>2506</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="B7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1">
+        <v>60</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
+      <c r="H7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="Q7" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
         <v>2507</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1">
+        <v>53</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="H8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1"/>
+    </row>
+    <row r="9" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
         <v>2508</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+      <c r="H9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
         <v>2509</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="H10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
         <v>2510</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1">
+        <v>52</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="H11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="O11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
         <v>2511</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1">
+        <v>53</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="H12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="O12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
         <v>2512</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1">
+        <v>57</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="H13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <v>2513</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="H14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="1"/>
+    </row>
+    <row r="15" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <v>2514</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="H15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
         <v>2515</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1">
+        <v>56</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+      <c r="H16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
         <v>2516</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1">
+        <v>55</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+      <c r="H17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="1"/>
+    </row>
+    <row r="18" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
         <v>2517</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="B18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1111111111114</v>
+      </c>
+      <c r="D18" s="1">
+        <v>55</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
+      <c r="H18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
         <v>2518</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="B19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="1">
+        <v>15</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
         <v>2519</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <v>55</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
+      <c r="H20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="1"/>
+    </row>
+    <row r="21" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
         <v>2520</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1">
+        <v>60</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="H21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="1"/>
+    </row>
+    <row r="22" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
         <v>2521</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="1">
+        <v>13</v>
+      </c>
+      <c r="D22" s="1">
+        <v>60</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+      <c r="H22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
         <v>2522</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1">
+        <v>14</v>
+      </c>
+      <c r="D23" s="1">
+        <v>56</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="H23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="1"/>
+    </row>
+    <row r="24" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
         <v>2523</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>14</v>
+      </c>
+      <c r="D24" s="1">
+        <v>66</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+      <c r="H24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
         <v>2524</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1">
+        <v>14</v>
+      </c>
+      <c r="D25" s="1">
+        <v>64</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+      <c r="H25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="1"/>
+    </row>
+    <row r="26" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
         <v>2525</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="1">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1">
+        <v>56</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+      <c r="H26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
         <v>2526</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="1">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1">
+        <v>58</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+      <c r="H27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
         <v>2527</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1">
+        <v>11</v>
+      </c>
+      <c r="D28" s="1">
+        <v>53</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
+      <c r="H28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="1"/>
+    </row>
+    <row r="29" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
         <v>2528</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="1">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1">
+        <v>60</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+      <c r="H29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
         <v>2529</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="1">
+        <v>11</v>
+      </c>
+      <c r="D30" s="1">
+        <v>54</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
+      <c r="H30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="1"/>
+    </row>
+    <row r="31" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
         <v>2530</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="1">
+        <v>11</v>
+      </c>
+      <c r="D31" s="1">
+        <v>60</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
+      <c r="H31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="1"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A33" s="10"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
